--- a/results/log_pv_cap/log_pv_cap_densities_pdensity_effects.xlsx
+++ b/results/log_pv_cap/log_pv_cap_densities_pdensity_effects.xlsx
@@ -511,388 +511,388 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pdensity</t>
+          <t>D(Population)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>0.565</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.002</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.540</t>
+          <t>0.569</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>0.081</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>-0.001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.082</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.001</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.075</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.018</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.002</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.016</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>0.003</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.054</t>
+          <t>2.905</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.496</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>2.912</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.005</t>
+          <t>4.765</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.079</t>
+          <t>0.403</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.084</t>
+          <t>4.362</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.215</t>
+          <t>4.963</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.070</t>
+          <t>0.558</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.145</t>
+          <t>4.405</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-2.030</t>
+          <t>1.737</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.382</t>
+          <t>1.051</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-1.648</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.090</t>
+          <t>4.100</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2.021</t>
+          <t>3.769</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3.428</t>
+          <t>4.297</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2.790</t>
+          <t>4.163</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>0.134</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.638</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.861</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.162</t>
+          <t>-0.222</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>0.805</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.034</t>
+          <t>-0.054</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>0.829</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.858</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.029</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.411</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.270</t>
+          <t>0.854</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>0.557</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.935</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.887</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.028</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.892</t>
+          <t>-0.971</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.034</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.857</t>
+          <t>-0.911</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.243</t>
+          <t>-0.292</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.122</t>
+          <t>-0.149</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>-0.142</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.268</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.061</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-0.207</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-0.120</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-0.073</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-0.047</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-0.132</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>-0.121</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.243</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.021</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-0.223</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.083</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-0.016</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-0.068</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.115</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.075</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-0.099</t>
+          <t>-0.128</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>-0.124</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.004</t>
         </is>
       </c>
     </row>
